--- a/Config/Excel/CardConfig.xlsx
+++ b/Config/Excel/CardConfig.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="TestConfig" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestConfig!$A$3:$E$60</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,18 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="184">
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>Pattern</t>
+    <t>Image</t>
   </si>
   <si>
     <t>Suit</t>
@@ -52,28 +49,33 @@
     <t>Rank</t>
   </si>
   <si>
+    <t>SingleGrab</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>注释</t>
   </si>
   <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>图标</t>
-  </si>
-  <si>
-    <t>纸牌中央图案</t>
+    <t>图片路径</t>
   </si>
   <si>
     <t>花色</t>
   </si>
   <si>
-    <t>点数</t>
+    <t>点数
+-1可以任意连接
+-2都不可以连接</t>
+  </si>
+  <si>
+    <t>是否默认单抓</t>
   </si>
   <si>
     <t>0100001</t>
@@ -82,10 +84,7 @@
     <t>红心A</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>suit:0</t>
+    <t>cardHeartsA</t>
   </si>
   <si>
     <t>0100002</t>
@@ -94,61 +93,88 @@
     <t>红心2</t>
   </si>
   <si>
+    <t>cardHearts2</t>
+  </si>
+  <si>
     <t>0100003</t>
   </si>
   <si>
     <t>红心3</t>
   </si>
   <si>
+    <t>cardHearts3</t>
+  </si>
+  <si>
     <t>0100004</t>
   </si>
   <si>
     <t>红心4</t>
   </si>
   <si>
+    <t>cardHearts4</t>
+  </si>
+  <si>
     <t>0100005</t>
   </si>
   <si>
     <t>红心5</t>
   </si>
   <si>
+    <t>cardHearts5</t>
+  </si>
+  <si>
     <t>0100006</t>
   </si>
   <si>
     <t>红心6</t>
   </si>
   <si>
+    <t>cardHearts6</t>
+  </si>
+  <si>
     <t>0100007</t>
   </si>
   <si>
     <t>红心7</t>
   </si>
   <si>
+    <t>cardHearts7</t>
+  </si>
+  <si>
     <t>0100008</t>
   </si>
   <si>
     <t>红心8</t>
   </si>
   <si>
+    <t>cardHearts8</t>
+  </si>
+  <si>
     <t>0100009</t>
   </si>
   <si>
     <t>红心9</t>
   </si>
   <si>
+    <t>cardHearts9</t>
+  </si>
+  <si>
     <t>0100010</t>
   </si>
   <si>
     <t>红心10</t>
   </si>
   <si>
+    <t>cardHearts10</t>
+  </si>
+  <si>
     <t>0100011</t>
   </si>
   <si>
     <t>红心J</t>
   </si>
   <si>
-    <t>J</t>
+    <t>cardHeartsJ</t>
   </si>
   <si>
     <t>0100012</t>
@@ -157,7 +183,7 @@
     <t>红心Q</t>
   </si>
   <si>
-    <t>Q</t>
+    <t>cardHeartsQ</t>
   </si>
   <si>
     <t>0100013</t>
@@ -166,7 +192,7 @@
     <t>红心K</t>
   </si>
   <si>
-    <t>K</t>
+    <t>cardHeartsK</t>
   </si>
   <si>
     <t>0101001</t>
@@ -175,7 +201,7 @@
     <t>梅花A</t>
   </si>
   <si>
-    <t>suit:1</t>
+    <t>cardClubsA</t>
   </si>
   <si>
     <t>0101002</t>
@@ -184,79 +210,115 @@
     <t>梅花2</t>
   </si>
   <si>
+    <t>cardClubs2</t>
+  </si>
+  <si>
     <t>0101003</t>
   </si>
   <si>
     <t>梅花3</t>
   </si>
   <si>
+    <t>cardClubs3</t>
+  </si>
+  <si>
     <t>0101004</t>
   </si>
   <si>
     <t>梅花4</t>
   </si>
   <si>
+    <t>cardClubs4</t>
+  </si>
+  <si>
     <t>0101005</t>
   </si>
   <si>
     <t>梅花5</t>
   </si>
   <si>
+    <t>cardClubs5</t>
+  </si>
+  <si>
     <t>0101006</t>
   </si>
   <si>
     <t>梅花6</t>
   </si>
   <si>
+    <t>cardClubs6</t>
+  </si>
+  <si>
     <t>0101007</t>
   </si>
   <si>
     <t>梅花7</t>
   </si>
   <si>
+    <t>cardClubs7</t>
+  </si>
+  <si>
     <t>0101008</t>
   </si>
   <si>
     <t>梅花8</t>
   </si>
   <si>
+    <t>cardClubs8</t>
+  </si>
+  <si>
     <t>0101009</t>
   </si>
   <si>
     <t>梅花9</t>
   </si>
   <si>
+    <t>cardClubs9</t>
+  </si>
+  <si>
     <t>0101010</t>
   </si>
   <si>
     <t>梅花10</t>
   </si>
   <si>
+    <t>cardClubs10</t>
+  </si>
+  <si>
     <t>0101011</t>
   </si>
   <si>
     <t>梅花J</t>
   </si>
   <si>
+    <t>cardClubsJ</t>
+  </si>
+  <si>
     <t>0101012</t>
   </si>
   <si>
     <t>梅花Q</t>
   </si>
   <si>
+    <t>cardClubsQ</t>
+  </si>
+  <si>
     <t>0101013</t>
   </si>
   <si>
     <t>梅花K</t>
   </si>
   <si>
+    <t>cardClubsK</t>
+  </si>
+  <si>
     <t>0102001</t>
   </si>
   <si>
     <t>黑桃A</t>
   </si>
   <si>
-    <t>suit:2</t>
+    <t>cardSpadesA</t>
   </si>
   <si>
     <t>0102002</t>
@@ -265,79 +327,115 @@
     <t>黑桃2</t>
   </si>
   <si>
+    <t>cardSpades2</t>
+  </si>
+  <si>
     <t>0102003</t>
   </si>
   <si>
     <t>黑桃3</t>
   </si>
   <si>
+    <t>cardSpades3</t>
+  </si>
+  <si>
     <t>0102004</t>
   </si>
   <si>
     <t>黑桃4</t>
   </si>
   <si>
+    <t>cardSpades4</t>
+  </si>
+  <si>
     <t>0102005</t>
   </si>
   <si>
     <t>黑桃5</t>
   </si>
   <si>
+    <t>cardSpades5</t>
+  </si>
+  <si>
     <t>0102006</t>
   </si>
   <si>
     <t>黑桃6</t>
   </si>
   <si>
+    <t>cardSpades6</t>
+  </si>
+  <si>
     <t>0102007</t>
   </si>
   <si>
     <t>黑桃7</t>
   </si>
   <si>
+    <t>cardSpades7</t>
+  </si>
+  <si>
     <t>0102008</t>
   </si>
   <si>
     <t>黑桃8</t>
   </si>
   <si>
+    <t>cardSpades8</t>
+  </si>
+  <si>
     <t>0102009</t>
   </si>
   <si>
     <t>黑桃9</t>
   </si>
   <si>
+    <t>cardSpades9</t>
+  </si>
+  <si>
     <t>0102010</t>
   </si>
   <si>
     <t>黑桃10</t>
   </si>
   <si>
+    <t>cardSpades10</t>
+  </si>
+  <si>
     <t>0102011</t>
   </si>
   <si>
     <t>黑桃J</t>
   </si>
   <si>
+    <t>cardSpadesJ</t>
+  </si>
+  <si>
     <t>0102012</t>
   </si>
   <si>
     <t>黑桃Q</t>
   </si>
   <si>
+    <t>cardSpadesQ</t>
+  </si>
+  <si>
     <t>0102013</t>
   </si>
   <si>
     <t>黑桃K</t>
   </si>
   <si>
+    <t>cardSpadesK</t>
+  </si>
+  <si>
     <t>0103001</t>
   </si>
   <si>
     <t>方块A</t>
   </si>
   <si>
-    <t>suit:3</t>
+    <t>cardDiamondsA</t>
   </si>
   <si>
     <t>0103002</t>
@@ -346,70 +444,151 @@
     <t>方块2</t>
   </si>
   <si>
+    <t>cardDiamonds2</t>
+  </si>
+  <si>
     <t>0103003</t>
   </si>
   <si>
     <t>方块3</t>
   </si>
   <si>
+    <t>cardDiamonds3</t>
+  </si>
+  <si>
     <t>0103004</t>
   </si>
   <si>
     <t>方块4</t>
   </si>
   <si>
+    <t>cardDiamonds4</t>
+  </si>
+  <si>
     <t>0103005</t>
   </si>
   <si>
     <t>方块5</t>
   </si>
   <si>
+    <t>cardDiamonds5</t>
+  </si>
+  <si>
     <t>0103006</t>
   </si>
   <si>
     <t>方块6</t>
   </si>
   <si>
+    <t>cardDiamonds6</t>
+  </si>
+  <si>
     <t>0103007</t>
   </si>
   <si>
     <t>方块7</t>
   </si>
   <si>
+    <t>cardDiamonds7</t>
+  </si>
+  <si>
     <t>0103008</t>
   </si>
   <si>
     <t>方块8</t>
   </si>
   <si>
+    <t>cardDiamonds8</t>
+  </si>
+  <si>
     <t>0103009</t>
   </si>
   <si>
     <t>方块9</t>
   </si>
   <si>
+    <t>cardDiamonds9</t>
+  </si>
+  <si>
     <t>0103010</t>
   </si>
   <si>
     <t>方块10</t>
   </si>
   <si>
+    <t>cardDiamonds10</t>
+  </si>
+  <si>
     <t>0103011</t>
   </si>
   <si>
     <t>方块J</t>
   </si>
   <si>
+    <t>cardDiamondsJ</t>
+  </si>
+  <si>
     <t>0103012</t>
   </si>
   <si>
     <t>方块Q</t>
   </si>
   <si>
+    <t>cardDiamondsQ</t>
+  </si>
+  <si>
     <t>0103013</t>
   </si>
   <si>
     <t>方块K</t>
+  </si>
+  <si>
+    <t>cardDiamondsK</t>
+  </si>
+  <si>
+    <t>0200001</t>
+  </si>
+  <si>
+    <t>红心蜘蛛</t>
+  </si>
+  <si>
+    <t>cardHeartsSpider</t>
+  </si>
+  <si>
+    <t>0200002</t>
+  </si>
+  <si>
+    <t>梅花蜘蛛</t>
+  </si>
+  <si>
+    <t>cardClubsSpider</t>
+  </si>
+  <si>
+    <t>0200003</t>
+  </si>
+  <si>
+    <t>黑桃蜘蛛</t>
+  </si>
+  <si>
+    <t>cardSpadesSpider</t>
+  </si>
+  <si>
+    <t>0200004</t>
+  </si>
+  <si>
+    <t>方块蜘蛛</t>
+  </si>
+  <si>
+    <t>cardDiamondsSpider</t>
+  </si>
+  <si>
+    <t>0200005</t>
+  </si>
+  <si>
+    <t>黑色</t>
+  </si>
+  <si>
+    <t>cardBlack</t>
   </si>
 </sst>
 </file>
@@ -1025,15 +1204,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1568,1276 +1756,1215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="13.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="18.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="16.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="29.2685185185185" customWidth="1"/>
+    <col min="4" max="4" width="14.0092592592593" customWidth="1"/>
+    <col min="5" max="5" width="26.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.7407407407407" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    </row>
+    <row r="3" ht="43.2" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7">
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>11</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21">
         <v>5</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8">
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>8</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>11</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>12</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>13</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2</v>
+      </c>
+      <c r="E34">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2</v>
+      </c>
+      <c r="E35">
         <v>6</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9">
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>7</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>9</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>11</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>12</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>13</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="3">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="3">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>138</v>
+      </c>
+      <c r="D45" s="3">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" s="3">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="3">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="3">
+        <v>3</v>
+      </c>
+      <c r="E48">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="3">
+        <v>3</v>
+      </c>
+      <c r="E49">
         <v>7</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="3">
+        <v>3</v>
+      </c>
+      <c r="E50">
         <v>8</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D51" s="3">
+        <v>3</v>
+      </c>
+      <c r="E51">
         <v>9</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="3">
+        <v>3</v>
+      </c>
+      <c r="E52">
         <v>10</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14">
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="3">
+        <v>3</v>
+      </c>
+      <c r="E53">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15">
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" s="3">
+        <v>3</v>
+      </c>
+      <c r="E54">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16">
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="3">
+        <v>3</v>
+      </c>
+      <c r="E55">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>-1</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57">
         <v>1</v>
       </c>
-      <c r="G17">
+      <c r="E57">
+        <v>-1</v>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" t="s">
+        <v>177</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>-1</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B59" t="s">
+        <v>179</v>
+      </c>
+      <c r="C59" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>-1</v>
+      </c>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" t="s">
+        <v>183</v>
+      </c>
+      <c r="D60">
+        <v>-1</v>
+      </c>
+      <c r="E60">
+        <v>-2</v>
+      </c>
+      <c r="F60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="1">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="1">
-        <v>4</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="1">
-        <v>5</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="1">
-        <v>6</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="1">
-        <v>7</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="1">
-        <v>9</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="1">
-        <v>10</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="1">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2</v>
-      </c>
-      <c r="G32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="1">
-        <v>4</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="1">
-        <v>5</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="1">
-        <v>6</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2</v>
-      </c>
-      <c r="G35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="1">
-        <v>7</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F36" s="1">
-        <v>2</v>
-      </c>
-      <c r="G36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="1">
-        <v>8</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" s="1">
-        <v>2</v>
-      </c>
-      <c r="G37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="1">
-        <v>9</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2</v>
-      </c>
-      <c r="G38">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="1">
-        <v>10</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2</v>
-      </c>
-      <c r="G39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F40" s="1">
-        <v>2</v>
-      </c>
-      <c r="G40">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2</v>
-      </c>
-      <c r="G41">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2</v>
-      </c>
-      <c r="G42">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F43" s="1">
-        <v>3</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="1">
-        <v>2</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F44" s="1">
-        <v>3</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" s="1">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F45" s="1">
-        <v>3</v>
-      </c>
-      <c r="G45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="1">
-        <v>4</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F46" s="1">
-        <v>3</v>
-      </c>
-      <c r="G46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="1">
-        <v>5</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F47" s="1">
-        <v>3</v>
-      </c>
-      <c r="G47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="1">
-        <v>6</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F48" s="1">
-        <v>3</v>
-      </c>
-      <c r="G48">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="1">
-        <v>7</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" s="1">
-        <v>3</v>
-      </c>
-      <c r="G49">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="1">
-        <v>8</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F50" s="1">
-        <v>3</v>
-      </c>
-      <c r="G50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="1">
-        <v>9</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F51" s="1">
-        <v>3</v>
-      </c>
-      <c r="G51">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="1">
-        <v>10</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F52" s="1">
-        <v>3</v>
-      </c>
-      <c r="G52">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F53" s="1">
-        <v>3</v>
-      </c>
-      <c r="G53">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F54" s="1">
-        <v>3</v>
-      </c>
-      <c r="G54">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F55" s="1">
-        <v>3</v>
-      </c>
-      <c r="G55">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:E60" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/Config/Excel/CardConfig.xlsx
+++ b/Config/Excel/CardConfig.xlsx
@@ -582,7 +582,7 @@
     <t>cardDiamondsSpider</t>
   </si>
   <si>
-    <t>0200005</t>
+    <t>0300005</t>
   </si>
   <si>
     <t>黑色</t>

--- a/Config/Excel/CardConfig.xlsx
+++ b/Config/Excel/CardConfig.xlsx
@@ -15,7 +15,7 @@
     <sheet name="TestConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestConfig!$A$3:$E$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestConfig!$A$3:$E$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="199">
   <si>
     <t>Id</t>
   </si>
@@ -49,9 +49,18 @@
     <t>Rank</t>
   </si>
   <si>
+    <t>Price</t>
+  </si>
+  <si>
     <t>SingleGrab</t>
   </si>
   <si>
+    <t>AnyTarget</t>
+  </si>
+  <si>
+    <t>PlaceSkill</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -67,7 +76,9 @@
     <t>图片路径</t>
   </si>
   <si>
-    <t>花色</t>
+    <t>花色
+-1可以任意花色
+-2没有花色</t>
   </si>
   <si>
     <t>点数
@@ -75,7 +86,54 @@
 -2都不可以连接</t>
   </si>
   <si>
-    <t>是否默认单抓</t>
+    <t>价值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否默认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单抓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否默认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任意放下</t>
+    </r>
+  </si>
+  <si>
+    <t>放下后技能</t>
   </si>
   <si>
     <t>0100001</t>
@@ -582,13 +640,40 @@
     <t>cardDiamondsSpider</t>
   </si>
   <si>
-    <t>0300005</t>
+    <t>0300001</t>
   </si>
   <si>
     <t>黑色</t>
   </si>
   <si>
     <t>cardBlack</t>
+  </si>
+  <si>
+    <t>0200005</t>
+  </si>
+  <si>
+    <t>蜘蛛</t>
+  </si>
+  <si>
+    <t>cardSpider</t>
+  </si>
+  <si>
+    <t>0200006</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>cardCopy</t>
+  </si>
+  <si>
+    <t>0200007</t>
+  </si>
+  <si>
+    <t>回收</t>
+  </si>
+  <si>
+    <t>cardRecycle</t>
   </si>
 </sst>
 </file>
@@ -601,7 +686,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,6 +836,13 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1204,7 +1296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1212,7 +1304,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1756,18 +1854,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:I63"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="29.2685185185185" customWidth="1"/>
-    <col min="4" max="4" width="14.0092592592593" customWidth="1"/>
+    <col min="4" max="4" width="22.0277777777778" customWidth="1"/>
     <col min="5" max="5" width="26.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.7407407407407" customWidth="1"/>
+    <col min="6" max="6" width="23.3796296296296" customWidth="1"/>
+    <col min="7" max="7" width="24.2407407407407" customWidth="1"/>
+    <col min="8" max="8" width="22.7037037037037" customWidth="1"/>
+    <col min="9" max="9" width="17.1018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1784,1092 +1885,1587 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="43.2" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="43.2" spans="1:9">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5">
         <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5">
         <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3">
+        <v>27</v>
+      </c>
+      <c r="D6" s="5">
         <v>0</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3">
+        <v>30</v>
+      </c>
+      <c r="D7" s="5">
         <v>0</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="3">
+        <v>33</v>
+      </c>
+      <c r="D8" s="5">
         <v>0</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="3">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5">
         <v>0</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>31</v>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="3">
+        <v>39</v>
+      </c>
+      <c r="D10" s="5">
         <v>0</v>
       </c>
       <c r="E10">
         <v>7</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>34</v>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="3">
+        <v>42</v>
+      </c>
+      <c r="D11" s="5">
         <v>0</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="3">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5">
         <v>0</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>40</v>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="3">
+        <v>48</v>
+      </c>
+      <c r="D13" s="5">
         <v>0</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>43</v>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="3">
+        <v>51</v>
+      </c>
+      <c r="D14" s="5">
         <v>0</v>
       </c>
       <c r="E14">
         <v>11</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>46</v>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="3">
+        <v>54</v>
+      </c>
+      <c r="D15" s="5">
         <v>0</v>
       </c>
       <c r="E15">
         <v>12</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>49</v>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="3">
+        <v>57</v>
+      </c>
+      <c r="D16" s="5">
         <v>0</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>52</v>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="3">
+        <v>60</v>
+      </c>
+      <c r="D17" s="5">
         <v>1</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>55</v>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="3">
+        <v>63</v>
+      </c>
+      <c r="D18" s="5">
         <v>1</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>58</v>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="3">
+        <v>66</v>
+      </c>
+      <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="4" t="s">
-        <v>61</v>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="3">
+        <v>69</v>
+      </c>
+      <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20">
         <v>4</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="4" t="s">
-        <v>64</v>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="3">
+        <v>72</v>
+      </c>
+      <c r="D21" s="5">
         <v>1</v>
       </c>
       <c r="E21">
         <v>5</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="4" t="s">
-        <v>67</v>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="3">
+        <v>75</v>
+      </c>
+      <c r="D22" s="5">
         <v>1</v>
       </c>
       <c r="E22">
         <v>6</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="4" t="s">
-        <v>70</v>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="3">
+        <v>78</v>
+      </c>
+      <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23">
         <v>7</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="4" t="s">
-        <v>73</v>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="3">
+        <v>81</v>
+      </c>
+      <c r="D24" s="5">
         <v>1</v>
       </c>
       <c r="E24">
         <v>8</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="4" t="s">
-        <v>76</v>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="3">
+        <v>84</v>
+      </c>
+      <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25">
         <v>9</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="4" t="s">
-        <v>79</v>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="3">
+        <v>87</v>
+      </c>
+      <c r="D26" s="5">
         <v>1</v>
       </c>
       <c r="E26">
         <v>10</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="4" t="s">
-        <v>82</v>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="3">
+        <v>90</v>
+      </c>
+      <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27">
         <v>11</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="4" t="s">
-        <v>85</v>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="3">
+        <v>93</v>
+      </c>
+      <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28">
         <v>12</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="4" t="s">
-        <v>88</v>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="3">
+        <v>96</v>
+      </c>
+      <c r="D29" s="5">
         <v>1</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="4" t="s">
-        <v>91</v>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="3">
+        <v>99</v>
+      </c>
+      <c r="D30" s="5">
         <v>2</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>94</v>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="3">
+        <v>102</v>
+      </c>
+      <c r="D31" s="5">
         <v>2</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>97</v>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="3">
+        <v>105</v>
+      </c>
+      <c r="D32" s="5">
         <v>2</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>100</v>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="3">
+        <v>108</v>
+      </c>
+      <c r="D33" s="5">
         <v>2</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="4" t="s">
-        <v>103</v>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="3">
+        <v>111</v>
+      </c>
+      <c r="D34" s="5">
         <v>2</v>
       </c>
       <c r="E34">
         <v>5</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>106</v>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="3">
+        <v>114</v>
+      </c>
+      <c r="D35" s="5">
         <v>2</v>
       </c>
       <c r="E35">
         <v>6</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="4" t="s">
-        <v>109</v>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="3">
+        <v>117</v>
+      </c>
+      <c r="D36" s="5">
         <v>2</v>
       </c>
       <c r="E36">
         <v>7</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="4" t="s">
-        <v>112</v>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="3">
+        <v>120</v>
+      </c>
+      <c r="D37" s="5">
         <v>2</v>
       </c>
       <c r="E37">
         <v>8</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="4" t="s">
-        <v>115</v>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" s="3">
+        <v>123</v>
+      </c>
+      <c r="D38" s="5">
         <v>2</v>
       </c>
       <c r="E38">
         <v>9</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="4" t="s">
-        <v>118</v>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="3">
+        <v>126</v>
+      </c>
+      <c r="D39" s="5">
         <v>2</v>
       </c>
       <c r="E39">
         <v>10</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="4" t="s">
-        <v>121</v>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" s="3">
+        <v>129</v>
+      </c>
+      <c r="D40" s="5">
         <v>2</v>
       </c>
       <c r="E40">
         <v>11</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="4" t="s">
-        <v>124</v>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="3">
+        <v>132</v>
+      </c>
+      <c r="D41" s="5">
         <v>2</v>
       </c>
       <c r="E41">
         <v>12</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="4" t="s">
-        <v>127</v>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
-      </c>
-      <c r="D42" s="3">
+        <v>135</v>
+      </c>
+      <c r="D42" s="5">
         <v>2</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="4" t="s">
-        <v>130</v>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="3">
+        <v>138</v>
+      </c>
+      <c r="D43" s="5">
         <v>3</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="4" t="s">
-        <v>133</v>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="3">
+        <v>141</v>
+      </c>
+      <c r="D44" s="5">
         <v>3</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="4" t="s">
-        <v>136</v>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="3">
+        <v>144</v>
+      </c>
+      <c r="D45" s="5">
         <v>3</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="4" t="s">
-        <v>139</v>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" s="3">
+        <v>147</v>
+      </c>
+      <c r="D46" s="5">
         <v>3</v>
       </c>
       <c r="E46">
         <v>4</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="4" t="s">
-        <v>142</v>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="3">
+        <v>150</v>
+      </c>
+      <c r="D47" s="5">
         <v>3</v>
       </c>
       <c r="E47">
         <v>5</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="4" t="s">
-        <v>145</v>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" s="3">
+        <v>153</v>
+      </c>
+      <c r="D48" s="5">
         <v>3</v>
       </c>
       <c r="E48">
         <v>6</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="4" t="s">
-        <v>148</v>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" s="3">
+        <v>156</v>
+      </c>
+      <c r="D49" s="5">
         <v>3</v>
       </c>
       <c r="E49">
         <v>7</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="4" t="s">
-        <v>151</v>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" s="3">
+        <v>159</v>
+      </c>
+      <c r="D50" s="5">
         <v>3</v>
       </c>
       <c r="E50">
         <v>8</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="4" t="s">
-        <v>154</v>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="3">
+        <v>162</v>
+      </c>
+      <c r="D51" s="5">
         <v>3</v>
       </c>
       <c r="E51">
         <v>9</v>
       </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="4" t="s">
-        <v>157</v>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
-      </c>
-      <c r="D52" s="3">
+        <v>165</v>
+      </c>
+      <c r="D52" s="5">
         <v>3</v>
       </c>
       <c r="E52">
         <v>10</v>
       </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="4" t="s">
-        <v>160</v>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="3">
+        <v>168</v>
+      </c>
+      <c r="D53" s="5">
         <v>3</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="4" t="s">
-        <v>163</v>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
-      </c>
-      <c r="D54" s="3">
+        <v>171</v>
+      </c>
+      <c r="D54" s="5">
         <v>3</v>
       </c>
       <c r="E54">
         <v>12</v>
       </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="4" t="s">
-        <v>166</v>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
-      </c>
-      <c r="D55" s="3">
+        <v>174</v>
+      </c>
+      <c r="D55" s="5">
         <v>3</v>
       </c>
       <c r="E55">
         <v>13</v>
       </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="5" t="s">
-        <v>169</v>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2877,19 +3473,28 @@
       <c r="E56">
         <v>-1</v>
       </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="5" t="s">
-        <v>172</v>
+      <c r="F56">
+        <v>150</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2897,19 +3502,28 @@
       <c r="E57">
         <v>-1</v>
       </c>
-      <c r="F57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="5" t="s">
-        <v>175</v>
+      <c r="F57">
+        <v>150</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="B58" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2917,19 +3531,28 @@
       <c r="E58">
         <v>-1</v>
       </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="5" t="s">
-        <v>178</v>
+      <c r="F58">
+        <v>150</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C59" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2937,32 +3560,137 @@
       <c r="E59">
         <v>-1</v>
       </c>
-      <c r="F59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="5" t="s">
-        <v>181</v>
+      <c r="F59">
+        <v>150</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="B60" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D60">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E60">
         <v>-2</v>
       </c>
-      <c r="F60" t="b">
+      <c r="F60">
+        <v>-70</v>
+      </c>
+      <c r="G60" t="b">
         <v>1</v>
       </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C61" t="s">
+        <v>192</v>
+      </c>
+      <c r="D61">
+        <v>-1</v>
+      </c>
+      <c r="E61">
+        <v>-1</v>
+      </c>
+      <c r="F61">
+        <v>350</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" t="s">
+        <v>194</v>
+      </c>
+      <c r="C62" t="s">
+        <v>195</v>
+      </c>
+      <c r="D62">
+        <v>-2</v>
+      </c>
+      <c r="E62">
+        <v>-2</v>
+      </c>
+      <c r="F62">
+        <v>150</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" t="s">
+        <v>198</v>
+      </c>
+      <c r="D63">
+        <v>-2</v>
+      </c>
+      <c r="E63">
+        <v>-2</v>
+      </c>
+      <c r="F63">
+        <v>80</v>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:E60" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:E63" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
